--- a/samples/charts.xlsx
+++ b/samples/charts.xlsx
@@ -319,7 +319,11 @@
           </val>
         </ser>
         <dLbls>
+          <showLegendKey val="0"/>
           <showVal val="1"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+          <showPercent val="0"/>
         </dLbls>
         <gapWidth val="150"/>
         <axId val="10"/>
@@ -885,6 +889,10 @@
           </val>
         </ser>
         <dLbls>
+          <showLegendKey val="0"/>
+          <showVal val="0"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
           <showPercent val="1"/>
         </dLbls>
         <firstSliceAng val="0"/>
